--- a/data/performance/daily/signal_list_2026-08-06.xlsx
+++ b/data/performance/daily/signal_list_2026-08-06.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-08-06.xlsx
+++ b/data/performance/daily/signal_list_2026-08-06.xlsx
@@ -559,7 +559,7 @@
         <v>1445</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>1445</v>
       </c>
       <c r="E5" t="n">
         <v>1430</v>
@@ -609,7 +609,7 @@
         <v>1425</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>1425</v>
       </c>
       <c r="E6" t="n">
         <v>1400</v>
@@ -659,7 +659,7 @@
         <v>123</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>123</v>
       </c>
       <c r="E7" t="n">
         <v>124</v>
@@ -709,7 +709,7 @@
         <v>645</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>645</v>
       </c>
       <c r="E8" t="n">
         <v>635</v>
@@ -759,7 +759,7 @@
         <v>935</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>935</v>
       </c>
       <c r="E9" t="n">
         <v>915</v>
@@ -809,7 +809,7 @@
         <v>790</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>790</v>
       </c>
       <c r="E10" t="n">
         <v>785</v>
@@ -859,7 +859,7 @@
         <v>520</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>520</v>
       </c>
       <c r="E11" t="n">
         <v>520</v>
@@ -909,7 +909,7 @@
         <v>1650</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>1645</v>
       </c>
       <c r="E12" t="n">
         <v>1655</v>
@@ -959,7 +959,7 @@
         <v>466</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>466</v>
       </c>
       <c r="E13" t="n">
         <v>450</v>
@@ -1009,7 +1009,7 @@
         <v>179</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>181</v>
       </c>
       <c r="E14" t="n">
         <v>179</v>
@@ -1059,7 +1059,7 @@
         <v>1900</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>1980</v>
       </c>
       <c r="E15" t="n">
         <v>1900</v>
@@ -1109,7 +1109,7 @@
         <v>81</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>81</v>
       </c>
       <c r="E16" t="n">
         <v>81</v>
@@ -1159,7 +1159,7 @@
         <v>615</v>
       </c>
       <c r="D17" t="n">
-        <v/>
+        <v>620</v>
       </c>
       <c r="E17" t="n">
         <v>605</v>
@@ -1209,7 +1209,7 @@
         <v>148</v>
       </c>
       <c r="D18" t="n">
-        <v/>
+        <v>148</v>
       </c>
       <c r="E18" t="n">
         <v>147</v>
@@ -1259,7 +1259,7 @@
         <v>86</v>
       </c>
       <c r="D19" t="n">
-        <v/>
+        <v>86</v>
       </c>
       <c r="E19" t="n">
         <v>85</v>
@@ -1309,7 +1309,7 @@
         <v>36</v>
       </c>
       <c r="D20" t="n">
-        <v/>
+        <v>38</v>
       </c>
       <c r="E20" t="n">
         <v>39</v>
@@ -1359,7 +1359,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v/>
+        <v>83</v>
       </c>
       <c r="E21" t="n">
         <v>81</v>
@@ -1409,7 +1409,7 @@
         <v>115</v>
       </c>
       <c r="D22" t="n">
-        <v/>
+        <v>115</v>
       </c>
       <c r="E22" t="n">
         <v>116</v>
@@ -1459,7 +1459,7 @@
         <v>122</v>
       </c>
       <c r="D23" t="n">
-        <v/>
+        <v>122</v>
       </c>
       <c r="E23" t="n">
         <v>114</v>
@@ -1509,7 +1509,7 @@
         <v>595</v>
       </c>
       <c r="D24" t="n">
-        <v/>
+        <v>560.76</v>
       </c>
       <c r="E24" t="n">
         <v>610</v>
@@ -1559,7 +1559,7 @@
         <v>1670</v>
       </c>
       <c r="D25" t="n">
-        <v/>
+        <v>1670</v>
       </c>
       <c r="E25" t="n">
         <v>1690</v>
@@ -1609,7 +1609,7 @@
         <v>133</v>
       </c>
       <c r="D26" t="n">
-        <v/>
+        <v>134</v>
       </c>
       <c r="E26" t="n">
         <v>132</v>
@@ -1659,7 +1659,7 @@
         <v>25</v>
       </c>
       <c r="D27" t="n">
-        <v/>
+        <v>27</v>
       </c>
       <c r="E27" t="n">
         <v>27</v>
@@ -1709,7 +1709,7 @@
         <v>1005</v>
       </c>
       <c r="D28" t="n">
-        <v/>
+        <v>1005</v>
       </c>
       <c r="E28" t="n">
         <v>1005</v>
@@ -1759,7 +1759,7 @@
         <v>1280</v>
       </c>
       <c r="D29" t="n">
-        <v/>
+        <v>1280</v>
       </c>
       <c r="E29" t="n">
         <v>1275</v>
@@ -1809,7 +1809,7 @@
         <v>230</v>
       </c>
       <c r="D30" t="n">
-        <v/>
+        <v>230</v>
       </c>
       <c r="E30" t="n">
         <v>236</v>
@@ -1859,7 +1859,7 @@
         <v>1795</v>
       </c>
       <c r="D31" t="n">
-        <v/>
+        <v>1754.66</v>
       </c>
       <c r="E31" t="n">
         <v>1780</v>
@@ -1909,7 +1909,7 @@
         <v>505</v>
       </c>
       <c r="D32" t="n">
-        <v/>
+        <v>510</v>
       </c>
       <c r="E32" t="n">
         <v>505</v>
@@ -1959,7 +1959,7 @@
         <v>3880</v>
       </c>
       <c r="D33" t="n">
-        <v/>
+        <v>3940</v>
       </c>
       <c r="E33" t="n">
         <v>3800</v>
@@ -2009,7 +2009,7 @@
         <v>535</v>
       </c>
       <c r="D34" t="n">
-        <v/>
+        <v>535</v>
       </c>
       <c r="E34" t="n">
         <v>510</v>
@@ -2059,7 +2059,7 @@
         <v>1490</v>
       </c>
       <c r="D35" t="n">
-        <v/>
+        <v>1500</v>
       </c>
       <c r="E35" t="n">
         <v>1495</v>
@@ -2109,7 +2109,7 @@
         <v>725</v>
       </c>
       <c r="D36" t="n">
-        <v/>
+        <v>725</v>
       </c>
       <c r="E36" t="n">
         <v>730</v>
@@ -2159,7 +2159,7 @@
         <v>1095</v>
       </c>
       <c r="D37" t="n">
-        <v/>
+        <v>1080.18</v>
       </c>
       <c r="E37" t="n">
         <v>1100</v>
@@ -2209,7 +2209,7 @@
         <v>750</v>
       </c>
       <c r="D38" t="n">
-        <v/>
+        <v>740</v>
       </c>
       <c r="E38" t="n">
         <v>730</v>
@@ -2259,7 +2259,7 @@
         <v>910</v>
       </c>
       <c r="D39" t="n">
-        <v/>
+        <v>910</v>
       </c>
       <c r="E39" t="n">
         <v>895</v>
@@ -2309,7 +2309,7 @@
         <v>122</v>
       </c>
       <c r="D40" t="n">
-        <v/>
+        <v>125</v>
       </c>
       <c r="E40" t="n">
         <v>129</v>
@@ -2359,7 +2359,7 @@
         <v>79</v>
       </c>
       <c r="D41" t="n">
-        <v/>
+        <v>79</v>
       </c>
       <c r="E41" t="n">
         <v>74</v>
@@ -2409,7 +2409,7 @@
         <v>440</v>
       </c>
       <c r="D42" t="n">
-        <v/>
+        <v>440</v>
       </c>
       <c r="E42" t="n">
         <v>436</v>
@@ -2459,7 +2459,7 @@
         <v>242</v>
       </c>
       <c r="D43" t="n">
-        <v/>
+        <v>246</v>
       </c>
       <c r="E43" t="n">
         <v>240</v>
@@ -2509,7 +2509,7 @@
         <v>87</v>
       </c>
       <c r="D44" t="n">
-        <v/>
+        <v>88</v>
       </c>
       <c r="E44" t="n">
         <v>87</v>
@@ -2559,7 +2559,7 @@
         <v>49</v>
       </c>
       <c r="D45" t="n">
-        <v/>
+        <v>50</v>
       </c>
       <c r="E45" t="n">
         <v>50</v>
@@ -2609,7 +2609,7 @@
         <v>2520</v>
       </c>
       <c r="D46" t="n">
-        <v/>
+        <v>2510</v>
       </c>
       <c r="E46" t="n">
         <v>2500</v>
@@ -2659,7 +2659,7 @@
         <v>79</v>
       </c>
       <c r="D47" t="n">
-        <v/>
+        <v>80</v>
       </c>
       <c r="E47" t="n">
         <v>81</v>
@@ -2709,7 +2709,7 @@
         <v>114</v>
       </c>
       <c r="D48" t="n">
-        <v/>
+        <v>113</v>
       </c>
       <c r="E48" t="n">
         <v>114</v>
@@ -2759,7 +2759,7 @@
         <v>172</v>
       </c>
       <c r="D49" t="n">
-        <v/>
+        <v>174</v>
       </c>
       <c r="E49" t="n">
         <v>195</v>
@@ -2809,7 +2809,7 @@
         <v>114</v>
       </c>
       <c r="D50" t="n">
-        <v/>
+        <v>112</v>
       </c>
       <c r="E50" t="n">
         <v>112</v>
@@ -2859,7 +2859,7 @@
         <v>167</v>
       </c>
       <c r="D51" t="n">
-        <v/>
+        <v>166</v>
       </c>
       <c r="E51" t="n">
         <v>173</v>
@@ -2909,7 +2909,7 @@
         <v>61</v>
       </c>
       <c r="D52" t="n">
-        <v/>
+        <v>61</v>
       </c>
       <c r="E52" t="n">
         <v>60</v>
@@ -2959,7 +2959,7 @@
         <v>535</v>
       </c>
       <c r="D53" t="n">
-        <v/>
+        <v>535</v>
       </c>
       <c r="E53" t="n">
         <v>540</v>
@@ -3009,7 +3009,7 @@
         <v>167</v>
       </c>
       <c r="D54" t="n">
-        <v/>
+        <v>167</v>
       </c>
       <c r="E54" t="n">
         <v>162</v>
@@ -3059,7 +3059,7 @@
         <v>108</v>
       </c>
       <c r="D55" t="n">
-        <v/>
+        <v>108</v>
       </c>
       <c r="E55" t="n">
         <v>109</v>
@@ -3109,7 +3109,7 @@
         <v>890</v>
       </c>
       <c r="D56" t="n">
-        <v/>
+        <v>900</v>
       </c>
       <c r="E56" t="n">
         <v>860</v>
@@ -3159,7 +3159,7 @@
         <v>149</v>
       </c>
       <c r="D57" t="n">
-        <v/>
+        <v>148.84</v>
       </c>
       <c r="E57" t="n">
         <v>155</v>
@@ -3209,7 +3209,7 @@
         <v>760</v>
       </c>
       <c r="D58" t="n">
-        <v/>
+        <v>760</v>
       </c>
       <c r="E58" t="n">
         <v>765</v>
@@ -3259,7 +3259,7 @@
         <v>720</v>
       </c>
       <c r="D59" t="n">
-        <v/>
+        <v>720</v>
       </c>
       <c r="E59" t="n">
         <v>720</v>
@@ -3309,7 +3309,7 @@
         <v>176</v>
       </c>
       <c r="D60" t="n">
-        <v/>
+        <v>176</v>
       </c>
       <c r="E60" t="n">
         <v>175</v>
@@ -3359,7 +3359,7 @@
         <v>200000</v>
       </c>
       <c r="D61" t="n">
-        <v/>
+        <v>200000</v>
       </c>
       <c r="E61" t="n">
         <v>200000</v>
@@ -3513,7 +3513,7 @@
         <v>1715</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>1885</v>
       </c>
       <c r="E5" t="n">
         <v>1885</v>
@@ -3563,7 +3563,7 @@
         <v>1715</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>1885</v>
       </c>
       <c r="E6" t="n">
         <v>1885</v>
@@ -3613,7 +3613,7 @@
         <v>1715</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>1885</v>
       </c>
       <c r="E7" t="n">
         <v>1885</v>
@@ -3663,7 +3663,7 @@
         <v>254</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>256</v>
       </c>
       <c r="E8" t="n">
         <v>248</v>
@@ -3713,7 +3713,7 @@
         <v>1425</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>1425</v>
       </c>
       <c r="E9" t="n">
         <v>1400</v>
@@ -3763,7 +3763,7 @@
         <v>3070</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>3170</v>
       </c>
       <c r="E10" t="n">
         <v>3080</v>
@@ -3813,7 +3813,7 @@
         <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>190</v>
       </c>
       <c r="E11" t="n">
         <v>191</v>
@@ -3863,7 +3863,7 @@
         <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>132</v>
       </c>
       <c r="E12" t="n">
         <v>132</v>
@@ -3913,7 +3913,7 @@
         <v>1340</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>1350</v>
       </c>
       <c r="E13" t="n">
         <v>1300</v>
@@ -3963,7 +3963,7 @@
         <v>438</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>438</v>
       </c>
       <c r="E14" t="n">
         <v>424</v>
@@ -4013,7 +4013,7 @@
         <v>123</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>123</v>
       </c>
       <c r="E15" t="n">
         <v>124</v>
@@ -4063,7 +4063,7 @@
         <v>645</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>645</v>
       </c>
       <c r="E16" t="n">
         <v>635</v>
@@ -4113,7 +4113,7 @@
         <v>118</v>
       </c>
       <c r="D17" t="n">
-        <v/>
+        <v>121</v>
       </c>
       <c r="E17" t="n">
         <v>119</v>
@@ -4163,7 +4163,7 @@
         <v>112</v>
       </c>
       <c r="D18" t="n">
-        <v/>
+        <v>112</v>
       </c>
       <c r="E18" t="n">
         <v>111</v>
@@ -4213,7 +4213,7 @@
         <v>935</v>
       </c>
       <c r="D19" t="n">
-        <v/>
+        <v>935</v>
       </c>
       <c r="E19" t="n">
         <v>915</v>
@@ -4263,7 +4263,7 @@
         <v>153</v>
       </c>
       <c r="D20" t="n">
-        <v/>
+        <v>153</v>
       </c>
       <c r="E20" t="n">
         <v>154</v>
@@ -4313,7 +4313,7 @@
         <v>685</v>
       </c>
       <c r="D21" t="n">
-        <v/>
+        <v>700</v>
       </c>
       <c r="E21" t="n">
         <v>695</v>
@@ -4363,7 +4363,7 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v/>
+        <v>73</v>
       </c>
       <c r="E22" t="n">
         <v>78</v>
@@ -4413,7 +4413,7 @@
         <v>610</v>
       </c>
       <c r="D23" t="n">
-        <v/>
+        <v>640</v>
       </c>
       <c r="E23" t="n">
         <v>610</v>
@@ -4463,7 +4463,7 @@
         <v>650</v>
       </c>
       <c r="D24" t="n">
-        <v/>
+        <v>650</v>
       </c>
       <c r="E24" t="n">
         <v>650</v>
@@ -4513,7 +4513,7 @@
         <v>220</v>
       </c>
       <c r="D25" t="n">
-        <v/>
+        <v>222</v>
       </c>
       <c r="E25" t="n">
         <v>218</v>
@@ -4563,7 +4563,7 @@
         <v>179</v>
       </c>
       <c r="D26" t="n">
-        <v/>
+        <v>181</v>
       </c>
       <c r="E26" t="n">
         <v>179</v>
@@ -4613,7 +4613,7 @@
         <v>90</v>
       </c>
       <c r="D27" t="n">
-        <v/>
+        <v>90</v>
       </c>
       <c r="E27" t="n">
         <v>92</v>
@@ -4663,7 +4663,7 @@
         <v>348</v>
       </c>
       <c r="D28" t="n">
-        <v/>
+        <v>350</v>
       </c>
       <c r="E28" t="n">
         <v>354</v>
@@ -4713,7 +4713,7 @@
         <v>615</v>
       </c>
       <c r="D29" t="n">
-        <v/>
+        <v>620</v>
       </c>
       <c r="E29" t="n">
         <v>605</v>
@@ -4763,7 +4763,7 @@
         <v>130</v>
       </c>
       <c r="D30" t="n">
-        <v/>
+        <v>130</v>
       </c>
       <c r="E30" t="n">
         <v>135</v>
@@ -4813,7 +4813,7 @@
         <v>116</v>
       </c>
       <c r="D31" t="n">
-        <v/>
+        <v>115</v>
       </c>
       <c r="E31" t="n">
         <v>111</v>
@@ -4863,7 +4863,7 @@
         <v>695</v>
       </c>
       <c r="D32" t="n">
-        <v/>
+        <v>695</v>
       </c>
       <c r="E32" t="n">
         <v>685</v>
@@ -4913,7 +4913,7 @@
         <v>86</v>
       </c>
       <c r="D33" t="n">
-        <v/>
+        <v>86</v>
       </c>
       <c r="E33" t="n">
         <v>85</v>
@@ -4963,7 +4963,7 @@
         <v>83</v>
       </c>
       <c r="D34" t="n">
-        <v/>
+        <v>83</v>
       </c>
       <c r="E34" t="n">
         <v>81</v>
@@ -5013,7 +5013,7 @@
         <v>316</v>
       </c>
       <c r="D35" t="n">
-        <v/>
+        <v>316</v>
       </c>
       <c r="E35" t="n">
         <v>388</v>
@@ -5063,7 +5063,7 @@
         <v>115</v>
       </c>
       <c r="D36" t="n">
-        <v/>
+        <v>115</v>
       </c>
       <c r="E36" t="n">
         <v>116</v>
@@ -5113,7 +5113,7 @@
         <v>107</v>
       </c>
       <c r="D37" t="n">
-        <v/>
+        <v>105</v>
       </c>
       <c r="E37" t="n">
         <v>107</v>
@@ -5163,7 +5163,7 @@
         <v>137</v>
       </c>
       <c r="D38" t="n">
-        <v/>
+        <v>137</v>
       </c>
       <c r="E38" t="n">
         <v>135</v>
@@ -5213,7 +5213,7 @@
         <v>875</v>
       </c>
       <c r="D39" t="n">
-        <v/>
+        <v>875</v>
       </c>
       <c r="E39" t="n">
         <v>825</v>
@@ -5263,7 +5263,7 @@
         <v>122</v>
       </c>
       <c r="D40" t="n">
-        <v/>
+        <v>122</v>
       </c>
       <c r="E40" t="n">
         <v>114</v>
@@ -5313,7 +5313,7 @@
         <v>5425</v>
       </c>
       <c r="D41" t="n">
-        <v/>
+        <v>5500</v>
       </c>
       <c r="E41" t="n">
         <v>5450</v>
@@ -5363,7 +5363,7 @@
         <v>286</v>
       </c>
       <c r="D42" t="n">
-        <v/>
+        <v>286</v>
       </c>
       <c r="E42" t="n">
         <v>278</v>
@@ -5413,7 +5413,7 @@
         <v>5300</v>
       </c>
       <c r="D43" t="n">
-        <v/>
+        <v>5350</v>
       </c>
       <c r="E43" t="n">
         <v>5325</v>
@@ -5463,7 +5463,7 @@
         <v>330</v>
       </c>
       <c r="D44" t="n">
-        <v/>
+        <v>330</v>
       </c>
       <c r="E44" t="n">
         <v>330</v>
@@ -5513,7 +5513,7 @@
         <v>800</v>
       </c>
       <c r="D45" t="n">
-        <v/>
+        <v>820</v>
       </c>
       <c r="E45" t="n">
         <v>790</v>
@@ -5563,7 +5563,7 @@
         <v>65</v>
       </c>
       <c r="D46" t="n">
-        <v/>
+        <v>65</v>
       </c>
       <c r="E46" t="n">
         <v>63</v>
@@ -5613,7 +5613,7 @@
         <v>114</v>
       </c>
       <c r="D47" t="n">
-        <v/>
+        <v>116</v>
       </c>
       <c r="E47" t="n">
         <v>113</v>
@@ -5663,7 +5663,7 @@
         <v>570</v>
       </c>
       <c r="D48" t="n">
-        <v/>
+        <v>570</v>
       </c>
       <c r="E48" t="n">
         <v>575</v>
@@ -5713,7 +5713,7 @@
         <v>825</v>
       </c>
       <c r="D49" t="n">
-        <v/>
+        <v>825</v>
       </c>
       <c r="E49" t="n">
         <v>845</v>
@@ -5763,7 +5763,7 @@
         <v>1670</v>
       </c>
       <c r="D50" t="n">
-        <v/>
+        <v>1670</v>
       </c>
       <c r="E50" t="n">
         <v>1690</v>
@@ -5813,7 +5813,7 @@
         <v>133</v>
       </c>
       <c r="D51" t="n">
-        <v/>
+        <v>134</v>
       </c>
       <c r="E51" t="n">
         <v>132</v>
@@ -5863,7 +5863,7 @@
         <v>2910</v>
       </c>
       <c r="D52" t="n">
-        <v/>
+        <v>2980</v>
       </c>
       <c r="E52" t="n">
         <v>2840</v>
@@ -5913,7 +5913,7 @@
         <v>1855</v>
       </c>
       <c r="D53" t="n">
-        <v/>
+        <v>1865</v>
       </c>
       <c r="E53" t="n">
         <v>1795</v>
@@ -5963,7 +5963,7 @@
         <v>210</v>
       </c>
       <c r="D54" t="n">
-        <v/>
+        <v>212</v>
       </c>
       <c r="E54" t="n">
         <v>212</v>
@@ -6013,7 +6013,7 @@
         <v>520</v>
       </c>
       <c r="D55" t="n">
-        <v/>
+        <v>520</v>
       </c>
       <c r="E55" t="n">
         <v>510</v>
@@ -6063,7 +6063,7 @@
         <v>202</v>
       </c>
       <c r="D56" t="n">
-        <v/>
+        <v>204</v>
       </c>
       <c r="E56" t="n">
         <v>200</v>
@@ -6113,7 +6113,7 @@
         <v>165</v>
       </c>
       <c r="D57" t="n">
-        <v/>
+        <v>165</v>
       </c>
       <c r="E57" t="n">
         <v>165</v>
@@ -6163,7 +6163,7 @@
         <v>535</v>
       </c>
       <c r="D58" t="n">
-        <v/>
+        <v>535</v>
       </c>
       <c r="E58" t="n">
         <v>530</v>
@@ -6213,7 +6213,7 @@
         <v>103</v>
       </c>
       <c r="D59" t="n">
-        <v/>
+        <v>103</v>
       </c>
       <c r="E59" t="n">
         <v>119</v>
@@ -6263,7 +6263,7 @@
         <v>100</v>
       </c>
       <c r="D60" t="n">
-        <v/>
+        <v>100</v>
       </c>
       <c r="E60" t="n">
         <v>99</v>
@@ -6313,7 +6313,7 @@
         <v>136</v>
       </c>
       <c r="D61" t="n">
-        <v/>
+        <v>137</v>
       </c>
       <c r="E61" t="n">
         <v>133</v>
@@ -6363,7 +6363,7 @@
         <v>230</v>
       </c>
       <c r="D62" t="n">
-        <v/>
+        <v>230</v>
       </c>
       <c r="E62" t="n">
         <v>236</v>
@@ -6413,7 +6413,7 @@
         <v>282</v>
       </c>
       <c r="D63" t="n">
-        <v/>
+        <v>286</v>
       </c>
       <c r="E63" t="n">
         <v>278</v>
@@ -6463,7 +6463,7 @@
         <v>950</v>
       </c>
       <c r="D64" t="n">
-        <v/>
+        <v>950</v>
       </c>
       <c r="E64" t="n">
         <v>975</v>
@@ -6513,7 +6513,7 @@
         <v>312</v>
       </c>
       <c r="D65" t="n">
-        <v/>
+        <v>312</v>
       </c>
       <c r="E65" t="n">
         <v>308</v>
@@ -6563,7 +6563,7 @@
         <v>218</v>
       </c>
       <c r="D66" t="n">
-        <v/>
+        <v>220</v>
       </c>
       <c r="E66" t="n">
         <v>212</v>
@@ -6613,7 +6613,7 @@
         <v>82</v>
       </c>
       <c r="D67" t="n">
-        <v/>
+        <v>82</v>
       </c>
       <c r="E67" t="n">
         <v>80</v>
@@ -6663,7 +6663,7 @@
         <v>62</v>
       </c>
       <c r="D68" t="n">
-        <v/>
+        <v>63</v>
       </c>
       <c r="E68" t="n">
         <v>66</v>
@@ -6713,7 +6713,7 @@
         <v>310</v>
       </c>
       <c r="D69" t="n">
-        <v/>
+        <v>311.45</v>
       </c>
       <c r="E69" t="n">
         <v>312</v>
@@ -6763,7 +6763,7 @@
         <v>1795</v>
       </c>
       <c r="D70" t="n">
-        <v/>
+        <v>1754.66</v>
       </c>
       <c r="E70" t="n">
         <v>1780</v>
@@ -6813,7 +6813,7 @@
         <v>505</v>
       </c>
       <c r="D71" t="n">
-        <v/>
+        <v>510</v>
       </c>
       <c r="E71" t="n">
         <v>505</v>
@@ -6863,7 +6863,7 @@
         <v>70</v>
       </c>
       <c r="D72" t="n">
-        <v/>
+        <v>71</v>
       </c>
       <c r="E72" t="n">
         <v>75</v>
@@ -6913,7 +6913,7 @@
         <v>1230</v>
       </c>
       <c r="D73" t="n">
-        <v/>
+        <v>1205</v>
       </c>
       <c r="E73" t="n">
         <v>1210</v>
@@ -6963,7 +6963,7 @@
         <v>3880</v>
       </c>
       <c r="D74" t="n">
-        <v/>
+        <v>3940</v>
       </c>
       <c r="E74" t="n">
         <v>3800</v>
@@ -7013,7 +7013,7 @@
         <v>127</v>
       </c>
       <c r="D75" t="n">
-        <v/>
+        <v>140</v>
       </c>
       <c r="E75" t="n">
         <v>159</v>
@@ -7063,7 +7063,7 @@
         <v>535</v>
       </c>
       <c r="D76" t="n">
-        <v/>
+        <v>535</v>
       </c>
       <c r="E76" t="n">
         <v>510</v>
@@ -7113,7 +7113,7 @@
         <v>1215</v>
       </c>
       <c r="D77" t="n">
-        <v/>
+        <v>1220</v>
       </c>
       <c r="E77" t="n">
         <v>1330</v>
@@ -7163,7 +7163,7 @@
         <v>595</v>
       </c>
       <c r="D78" t="n">
-        <v/>
+        <v>595</v>
       </c>
       <c r="E78" t="n">
         <v>610</v>
@@ -7213,7 +7213,7 @@
         <v>1490</v>
       </c>
       <c r="D79" t="n">
-        <v/>
+        <v>1500</v>
       </c>
       <c r="E79" t="n">
         <v>1495</v>
@@ -7263,7 +7263,7 @@
         <v>1845</v>
       </c>
       <c r="D80" t="n">
-        <v/>
+        <v>1845</v>
       </c>
       <c r="E80" t="n">
         <v>1805</v>
@@ -7313,7 +7313,7 @@
         <v>2070</v>
       </c>
       <c r="D81" t="n">
-        <v/>
+        <v>2070</v>
       </c>
       <c r="E81" t="n">
         <v>2050</v>
@@ -7363,7 +7363,7 @@
         <v>102</v>
       </c>
       <c r="D82" t="n">
-        <v/>
+        <v>102</v>
       </c>
       <c r="E82" t="n">
         <v>100</v>
@@ -7413,7 +7413,7 @@
         <v>1670</v>
       </c>
       <c r="D83" t="n">
-        <v/>
+        <v>1700</v>
       </c>
       <c r="E83" t="n">
         <v>1685</v>
@@ -7463,7 +7463,7 @@
         <v>2000</v>
       </c>
       <c r="D84" t="n">
-        <v/>
+        <v>2100</v>
       </c>
       <c r="E84" t="n">
         <v>2120</v>
@@ -7513,7 +7513,7 @@
         <v>1095</v>
       </c>
       <c r="D85" t="n">
-        <v/>
+        <v>1080.18</v>
       </c>
       <c r="E85" t="n">
         <v>1100</v>
@@ -7563,7 +7563,7 @@
         <v>98</v>
       </c>
       <c r="D86" t="n">
-        <v/>
+        <v>98</v>
       </c>
       <c r="E86" t="n">
         <v>102</v>
@@ -7613,7 +7613,7 @@
         <v>725</v>
       </c>
       <c r="D87" t="n">
-        <v/>
+        <v>710</v>
       </c>
       <c r="E87" t="n">
         <v>710</v>
@@ -7663,7 +7663,7 @@
         <v>1325</v>
       </c>
       <c r="D88" t="n">
-        <v/>
+        <v>1350</v>
       </c>
       <c r="E88" t="n">
         <v>1415</v>
@@ -7713,7 +7713,7 @@
         <v>675</v>
       </c>
       <c r="D89" t="n">
-        <v/>
+        <v>775</v>
       </c>
       <c r="E89" t="n">
         <v>670</v>
@@ -7763,7 +7763,7 @@
         <v>675</v>
       </c>
       <c r="D90" t="n">
-        <v/>
+        <v>685</v>
       </c>
       <c r="E90" t="n">
         <v>675</v>
@@ -7813,7 +7813,7 @@
         <v>78</v>
       </c>
       <c r="D91" t="n">
-        <v/>
+        <v>79</v>
       </c>
       <c r="E91" t="n">
         <v>80</v>
@@ -7863,7 +7863,7 @@
         <v>6400</v>
       </c>
       <c r="D92" t="n">
-        <v/>
+        <v>6325</v>
       </c>
       <c r="E92" t="n">
         <v>6300</v>
@@ -7913,7 +7913,7 @@
         <v>178</v>
       </c>
       <c r="D93" t="n">
-        <v/>
+        <v>182</v>
       </c>
       <c r="E93" t="n">
         <v>176</v>
@@ -7963,7 +7963,7 @@
         <v>12750</v>
       </c>
       <c r="D94" t="n">
-        <v/>
+        <v>12775</v>
       </c>
       <c r="E94" t="n">
         <v>12050</v>
@@ -8013,7 +8013,7 @@
         <v>140</v>
       </c>
       <c r="D95" t="n">
-        <v/>
+        <v>139</v>
       </c>
       <c r="E95" t="n">
         <v>139</v>
@@ -8063,7 +8063,7 @@
         <v>60</v>
       </c>
       <c r="D96" t="n">
-        <v/>
+        <v>59</v>
       </c>
       <c r="E96" t="n">
         <v>60</v>
@@ -8113,7 +8113,7 @@
         <v>139</v>
       </c>
       <c r="D97" t="n">
-        <v/>
+        <v>140</v>
       </c>
       <c r="E97" t="n">
         <v>138</v>
@@ -8163,7 +8163,7 @@
         <v>115</v>
       </c>
       <c r="D98" t="n">
-        <v/>
+        <v>114</v>
       </c>
       <c r="E98" t="n">
         <v>115</v>
@@ -8213,7 +8213,7 @@
         <v>2700</v>
       </c>
       <c r="D99" t="n">
-        <v/>
+        <v>2630</v>
       </c>
       <c r="E99" t="n">
         <v>2800</v>
@@ -8263,7 +8263,7 @@
         <v>147</v>
       </c>
       <c r="D100" t="n">
-        <v/>
+        <v>147</v>
       </c>
       <c r="E100" t="n">
         <v>143</v>
@@ -8313,7 +8313,7 @@
         <v>93</v>
       </c>
       <c r="D101" t="n">
-        <v/>
+        <v>91.95999999999999</v>
       </c>
       <c r="E101" t="n">
         <v>93</v>
@@ -8363,7 +8363,7 @@
         <v>171</v>
       </c>
       <c r="D102" t="n">
-        <v/>
+        <v>173</v>
       </c>
       <c r="E102" t="n">
         <v>188</v>
@@ -8413,7 +8413,7 @@
         <v>910</v>
       </c>
       <c r="D103" t="n">
-        <v/>
+        <v>910</v>
       </c>
       <c r="E103" t="n">
         <v>895</v>
@@ -8463,7 +8463,7 @@
         <v>122</v>
       </c>
       <c r="D104" t="n">
-        <v/>
+        <v>125</v>
       </c>
       <c r="E104" t="n">
         <v>129</v>
@@ -8513,7 +8513,7 @@
         <v>79</v>
       </c>
       <c r="D105" t="n">
-        <v/>
+        <v>79</v>
       </c>
       <c r="E105" t="n">
         <v>74</v>
@@ -8563,7 +8563,7 @@
         <v>61</v>
       </c>
       <c r="D106" t="n">
-        <v/>
+        <v>60</v>
       </c>
       <c r="E106" t="n">
         <v>61</v>
@@ -8613,7 +8613,7 @@
         <v>580</v>
       </c>
       <c r="D107" t="n">
-        <v/>
+        <v>575</v>
       </c>
       <c r="E107" t="n">
         <v>575</v>
@@ -8663,7 +8663,7 @@
         <v>830</v>
       </c>
       <c r="D108" t="n">
-        <v/>
+        <v>910</v>
       </c>
       <c r="E108" t="n">
         <v>910</v>
@@ -8713,7 +8713,7 @@
         <v>440</v>
       </c>
       <c r="D109" t="n">
-        <v/>
+        <v>440</v>
       </c>
       <c r="E109" t="n">
         <v>436</v>
@@ -8763,7 +8763,7 @@
         <v>360</v>
       </c>
       <c r="D110" t="n">
-        <v/>
+        <v>360</v>
       </c>
       <c r="E110" t="n">
         <v>358</v>
@@ -8813,7 +8813,7 @@
         <v>242</v>
       </c>
       <c r="D111" t="n">
-        <v/>
+        <v>246</v>
       </c>
       <c r="E111" t="n">
         <v>240</v>
@@ -8863,7 +8863,7 @@
         <v>77</v>
       </c>
       <c r="D112" t="n">
-        <v/>
+        <v>77</v>
       </c>
       <c r="E112" t="n">
         <v>78</v>
@@ -8913,7 +8913,7 @@
         <v>2520</v>
       </c>
       <c r="D113" t="n">
-        <v/>
+        <v>2510</v>
       </c>
       <c r="E113" t="n">
         <v>2500</v>
@@ -8963,7 +8963,7 @@
         <v>232</v>
       </c>
       <c r="D114" t="n">
-        <v/>
+        <v>234</v>
       </c>
       <c r="E114" t="n">
         <v>226</v>
@@ -9013,7 +9013,7 @@
         <v>480</v>
       </c>
       <c r="D115" t="n">
-        <v/>
+        <v>480</v>
       </c>
       <c r="E115" t="n">
         <v>472</v>
@@ -9063,7 +9063,7 @@
         <v>79</v>
       </c>
       <c r="D116" t="n">
-        <v/>
+        <v>80</v>
       </c>
       <c r="E116" t="n">
         <v>81</v>
@@ -9113,7 +9113,7 @@
         <v>585</v>
       </c>
       <c r="D117" t="n">
-        <v/>
+        <v>590</v>
       </c>
       <c r="E117" t="n">
         <v>580</v>
@@ -9163,7 +9163,7 @@
         <v>114</v>
       </c>
       <c r="D118" t="n">
-        <v/>
+        <v>113</v>
       </c>
       <c r="E118" t="n">
         <v>114</v>
@@ -9213,7 +9213,7 @@
         <v>1155</v>
       </c>
       <c r="D119" t="n">
-        <v/>
+        <v>1195</v>
       </c>
       <c r="E119" t="n">
         <v>1180</v>
@@ -9263,7 +9263,7 @@
         <v>172</v>
       </c>
       <c r="D120" t="n">
-        <v/>
+        <v>174</v>
       </c>
       <c r="E120" t="n">
         <v>195</v>
@@ -9313,7 +9313,7 @@
         <v>67</v>
       </c>
       <c r="D121" t="n">
-        <v/>
+        <v>67</v>
       </c>
       <c r="E121" t="n">
         <v>68</v>
@@ -9363,7 +9363,7 @@
         <v>167</v>
       </c>
       <c r="D122" t="n">
-        <v/>
+        <v>166</v>
       </c>
       <c r="E122" t="n">
         <v>173</v>
@@ -9413,7 +9413,7 @@
         <v>1615</v>
       </c>
       <c r="D123" t="n">
-        <v/>
+        <v>1620</v>
       </c>
       <c r="E123" t="n">
         <v>1595</v>
@@ -9463,7 +9463,7 @@
         <v>61</v>
       </c>
       <c r="D124" t="n">
-        <v/>
+        <v>61</v>
       </c>
       <c r="E124" t="n">
         <v>60</v>
@@ -9513,7 +9513,7 @@
         <v>63</v>
       </c>
       <c r="D125" t="n">
-        <v/>
+        <v>64</v>
       </c>
       <c r="E125" t="n">
         <v>63</v>
@@ -9563,7 +9563,7 @@
         <v>535</v>
       </c>
       <c r="D126" t="n">
-        <v/>
+        <v>535</v>
       </c>
       <c r="E126" t="n">
         <v>540</v>
@@ -9613,7 +9613,7 @@
         <v>230</v>
       </c>
       <c r="D127" t="n">
-        <v/>
+        <v>232</v>
       </c>
       <c r="E127" t="n">
         <v>228</v>
@@ -9663,7 +9663,7 @@
         <v>480</v>
       </c>
       <c r="D128" t="n">
-        <v/>
+        <v>480</v>
       </c>
       <c r="E128" t="n">
         <v>464</v>
@@ -9713,7 +9713,7 @@
         <v>73</v>
       </c>
       <c r="D129" t="n">
-        <v/>
+        <v>75</v>
       </c>
       <c r="E129" t="n">
         <v>75</v>
@@ -9763,7 +9763,7 @@
         <v>440</v>
       </c>
       <c r="D130" t="n">
-        <v/>
+        <v>456</v>
       </c>
       <c r="E130" t="n">
         <v>505</v>
@@ -9813,7 +9813,7 @@
         <v>94</v>
       </c>
       <c r="D131" t="n">
-        <v/>
+        <v>94</v>
       </c>
       <c r="E131" t="n">
         <v>92</v>
@@ -9863,7 +9863,7 @@
         <v>370</v>
       </c>
       <c r="D132" t="n">
-        <v/>
+        <v>372</v>
       </c>
       <c r="E132" t="n">
         <v>362</v>
@@ -9913,7 +9913,7 @@
         <v>167</v>
       </c>
       <c r="D133" t="n">
-        <v/>
+        <v>167</v>
       </c>
       <c r="E133" t="n">
         <v>162</v>
@@ -9963,7 +9963,7 @@
         <v>890</v>
       </c>
       <c r="D134" t="n">
-        <v/>
+        <v>900</v>
       </c>
       <c r="E134" t="n">
         <v>860</v>
@@ -10013,7 +10013,7 @@
         <v>4420</v>
       </c>
       <c r="D135" t="n">
-        <v/>
+        <v>4480</v>
       </c>
       <c r="E135" t="n">
         <v>4320</v>
@@ -10063,7 +10063,7 @@
         <v>238</v>
       </c>
       <c r="D136" t="n">
-        <v/>
+        <v>240</v>
       </c>
       <c r="E136" t="n">
         <v>232</v>
@@ -10113,7 +10113,7 @@
         <v>150</v>
       </c>
       <c r="D137" t="n">
-        <v/>
+        <v>152</v>
       </c>
       <c r="E137" t="n">
         <v>150</v>
@@ -10163,7 +10163,7 @@
         <v>149</v>
       </c>
       <c r="D138" t="n">
-        <v/>
+        <v>148.84</v>
       </c>
       <c r="E138" t="n">
         <v>155</v>
@@ -10213,7 +10213,7 @@
         <v>102</v>
       </c>
       <c r="D139" t="n">
-        <v/>
+        <v>102</v>
       </c>
       <c r="E139" t="n">
         <v>97</v>
@@ -10263,7 +10263,7 @@
         <v>318</v>
       </c>
       <c r="D140" t="n">
-        <v/>
+        <v>318</v>
       </c>
       <c r="E140" t="n">
         <v>322</v>
@@ -10313,7 +10313,7 @@
         <v>147</v>
       </c>
       <c r="D141" t="n">
-        <v/>
+        <v>148</v>
       </c>
       <c r="E141" t="n">
         <v>152</v>
@@ -10363,7 +10363,7 @@
         <v>101</v>
       </c>
       <c r="D142" t="n">
-        <v/>
+        <v>101</v>
       </c>
       <c r="E142" t="n">
         <v>99</v>
@@ -10413,7 +10413,7 @@
         <v>795</v>
       </c>
       <c r="D143" t="n">
-        <v/>
+        <v>795</v>
       </c>
       <c r="E143" t="n">
         <v>800</v>
@@ -10463,7 +10463,7 @@
         <v>950</v>
       </c>
       <c r="D144" t="n">
-        <v/>
+        <v>950</v>
       </c>
       <c r="E144" t="n">
         <v>945</v>
@@ -10513,7 +10513,7 @@
         <v>282</v>
       </c>
       <c r="D145" t="n">
-        <v/>
+        <v>282</v>
       </c>
       <c r="E145" t="n">
         <v>280</v>
@@ -10563,7 +10563,7 @@
         <v>142</v>
       </c>
       <c r="D146" t="n">
-        <v/>
+        <v>141</v>
       </c>
       <c r="E146" t="n">
         <v>137</v>
@@ -10613,7 +10613,7 @@
         <v>167</v>
       </c>
       <c r="D147" t="n">
-        <v/>
+        <v>167</v>
       </c>
       <c r="E147" t="n">
         <v>169</v>
@@ -10663,7 +10663,7 @@
         <v>156</v>
       </c>
       <c r="D148" t="n">
-        <v/>
+        <v>156</v>
       </c>
       <c r="E148" t="n">
         <v>156</v>
@@ -10713,7 +10713,7 @@
         <v>368</v>
       </c>
       <c r="D149" t="n">
-        <v/>
+        <v>368</v>
       </c>
       <c r="E149" t="n">
         <v>372</v>
@@ -10763,7 +10763,7 @@
         <v>308</v>
       </c>
       <c r="D150" t="n">
-        <v/>
+        <v>308</v>
       </c>
       <c r="E150" t="n">
         <v>312</v>
@@ -10813,7 +10813,7 @@
         <v>3880</v>
       </c>
       <c r="D151" t="n">
-        <v/>
+        <v>3880</v>
       </c>
       <c r="E151" t="n">
         <v>3810</v>
@@ -10863,7 +10863,7 @@
         <v>720</v>
       </c>
       <c r="D152" t="n">
-        <v/>
+        <v>725</v>
       </c>
       <c r="E152" t="n">
         <v>705</v>
@@ -10913,7 +10913,7 @@
         <v>115</v>
       </c>
       <c r="D153" t="n">
-        <v/>
+        <v>112</v>
       </c>
       <c r="E153" t="n">
         <v>113</v>
@@ -10963,7 +10963,7 @@
         <v>7400</v>
       </c>
       <c r="D154" t="n">
-        <v/>
+        <v>7600</v>
       </c>
       <c r="E154" t="n">
         <v>7575</v>
@@ -11013,7 +11013,7 @@
         <v>177</v>
       </c>
       <c r="D155" t="n">
-        <v/>
+        <v>180</v>
       </c>
       <c r="E155" t="n">
         <v>176</v>
@@ -11063,7 +11063,7 @@
         <v>655</v>
       </c>
       <c r="D156" t="n">
-        <v/>
+        <v>655</v>
       </c>
       <c r="E156" t="n">
         <v>675</v>
@@ -11113,7 +11113,7 @@
         <v>96</v>
       </c>
       <c r="D157" t="n">
-        <v/>
+        <v>97</v>
       </c>
       <c r="E157" t="n">
         <v>96</v>
@@ -11163,7 +11163,7 @@
         <v>765</v>
       </c>
       <c r="D158" t="n">
-        <v/>
+        <v>770</v>
       </c>
       <c r="E158" t="n">
         <v>775</v>
@@ -11213,7 +11213,7 @@
         <v>160</v>
       </c>
       <c r="D159" t="n">
-        <v/>
+        <v>160</v>
       </c>
       <c r="E159" t="n">
         <v>162</v>
@@ -11263,7 +11263,7 @@
         <v>940</v>
       </c>
       <c r="D160" t="n">
-        <v/>
+        <v>950</v>
       </c>
       <c r="E160" t="n">
         <v>935</v>
@@ -11313,7 +11313,7 @@
         <v>550</v>
       </c>
       <c r="D161" t="n">
-        <v/>
+        <v>555</v>
       </c>
       <c r="E161" t="n">
         <v>530</v>
@@ -11363,7 +11363,7 @@
         <v>272</v>
       </c>
       <c r="D162" t="n">
-        <v/>
+        <v>274</v>
       </c>
       <c r="E162" t="n">
         <v>264</v>
@@ -11413,7 +11413,7 @@
         <v>176</v>
       </c>
       <c r="D163" t="n">
-        <v/>
+        <v>176</v>
       </c>
       <c r="E163" t="n">
         <v>175</v>
@@ -11463,7 +11463,7 @@
         <v>200000</v>
       </c>
       <c r="D164" t="n">
-        <v/>
+        <v>200000</v>
       </c>
       <c r="E164" t="n">
         <v>200000</v>
@@ -11513,7 +11513,7 @@
         <v>615</v>
       </c>
       <c r="D165" t="n">
-        <v/>
+        <v>615</v>
       </c>
       <c r="E165" t="n">
         <v>585</v>
@@ -11563,7 +11563,7 @@
         <v>96</v>
       </c>
       <c r="D166" t="n">
-        <v/>
+        <v>96</v>
       </c>
       <c r="E166" t="n">
         <v>94</v>
